--- a/data/product.xlsx
+++ b/data/product.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wipro capstone\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8D54C0-85C5-4052-BABF-FF4FC013F554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD834E9B-F3E9-4BD1-BF5E-9692A54B9752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A6CED512-6857-43CF-8A33-2C777F08C651}"/>
   </bookViews>
@@ -34,23 +34,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>test_case</t>
   </si>
   <si>
-    <t>product_name</t>
-  </si>
-  <si>
-    <t>expected_result</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve"> type</t>
-  </si>
-  <si>
     <t>TC_01</t>
   </si>
   <si>
@@ -63,22 +54,85 @@
     <t>TC_04</t>
   </si>
   <si>
-    <t>POSITIVE</t>
-  </si>
-  <si>
-    <t>E2E</t>
-  </si>
-  <si>
-    <t>LIP BALM</t>
-  </si>
-  <si>
     <t>TC_05</t>
   </si>
   <si>
     <t>TC_06</t>
   </si>
   <si>
-    <t>NEGATIVE</t>
+    <t>TC_07</t>
+  </si>
+  <si>
+    <t>TestCaseName</t>
+  </si>
+  <si>
+    <t>hover beauty menu</t>
+  </si>
+  <si>
+    <t>homepage to beauty product</t>
+  </si>
+  <si>
+    <t>opening lip balm listing page</t>
+  </si>
+  <si>
+    <t>lipbalm to cart</t>
+  </si>
+  <si>
+    <t>invalid search in beauty section</t>
+  </si>
+  <si>
+    <t>invalid size</t>
+  </si>
+  <si>
+    <t>end to end</t>
+  </si>
+  <si>
+    <t>test type</t>
+  </si>
+  <si>
+    <t>positive</t>
+  </si>
+  <si>
+    <t>negative</t>
+  </si>
+  <si>
+    <t>expected result</t>
+  </si>
+  <si>
+    <t>hovering n beauty menu</t>
+  </si>
+  <si>
+    <t>lip balm lists page opens</t>
+  </si>
+  <si>
+    <t>lipbalm goes to cart successfully</t>
+  </si>
+  <si>
+    <t>gives products instead of displaying none</t>
+  </si>
+  <si>
+    <t>without size wont go to cart</t>
+  </si>
+  <si>
+    <t>from homepage to login page</t>
+  </si>
+  <si>
+    <t>beauty product opening</t>
+  </si>
+  <si>
+    <t>module</t>
+  </si>
+  <si>
+    <t>beauty</t>
+  </si>
+  <si>
+    <t>lip balm</t>
+  </si>
+  <si>
+    <t>minimalist vitamin c serum</t>
+  </si>
+  <si>
+    <t>xyz999lipbalm</t>
   </si>
 </sst>
 </file>
@@ -430,83 +484,146 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF77EA0-1C44-4B17-A240-0229C58BD788}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
